--- a/test/appn-simple.xlsx
+++ b/test/appn-simple.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -35,6 +35,9 @@
     <t xml:space="preserve">relatedMatch</t>
   </si>
   <si>
+    <t xml:space="preserve">forBiologicalMaterial</t>
+  </si>
+  <si>
     <t xml:space="preserve">growth stage</t>
   </si>
   <si>
@@ -47,6 +50,9 @@
     <t xml:space="preserve">http://purl.obolibrary.org/obo/PPO_0000013</t>
   </si>
   <si>
+    <t xml:space="preserve">any plant</t>
+  </si>
+  <si>
     <t xml:space="preserve">overall stature</t>
   </si>
   <si>
@@ -59,6 +65,9 @@
     <t xml:space="preserve">http://purl.obolibrary.org/obo/TO_0002756</t>
   </si>
   <si>
+    <t xml:space="preserve">grain</t>
+  </si>
+  <si>
     <t xml:space="preserve">scientificName</t>
   </si>
   <si>
@@ -68,9 +77,6 @@
     <t xml:space="preserve">exactMatch</t>
   </si>
   <si>
-    <t xml:space="preserve">any plant</t>
-  </si>
-  <si>
     <t xml:space="preserve">Plantae</t>
   </si>
   <si>
@@ -78,9 +84,6 @@
   </si>
   <si>
     <t xml:space="preserve">http://purl.obolibrary.org/obo/NCBITaxon_33090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grain</t>
   </si>
   <si>
     <t xml:space="preserve">Poaceae</t>
@@ -181,14 +184,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF468A1A"/>
-        <bgColor rgb="FF808000"/>
+        <fgColor rgb="FFDEE6EF"/>
+        <bgColor rgb="FFF6F9D4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDEE6EF"/>
-        <bgColor rgb="FFF6F9D4"/>
+        <fgColor rgb="FF468A1A"/>
+        <bgColor rgb="FF808000"/>
       </patternFill>
     </fill>
     <fill>
@@ -248,56 +251,56 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -558,181 +561,189 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="104"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="47.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="5.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="5.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="5.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="29.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="5.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="22.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="5.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="33.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="5.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="26.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="5.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="2" width="32.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="2" width="5.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="2" width="18.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="2" width="5.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="2" width="22.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="2" width="5.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="2" width="25.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="2" width="5.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="2" width="41.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="2" width="5.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="2" width="43.67"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="33" min="30" style="2" width="11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="43" min="34" style="3" width="11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16356" min="44" style="2" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16365" min="16357" style="2" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16369" min="16366" style="0" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16370" style="0" width="9.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="18.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="5.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="5.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="5.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="3" width="29.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="3" width="5.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="22.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="3" width="5.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="3" width="33.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="3" width="5.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="3" width="26.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="3" width="5.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="3" width="32.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="3" width="5.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="3" width="18.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="3" width="5.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="3" width="22.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="3" width="5.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="3" width="25.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="3" width="5.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="3" width="41.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="3" width="5.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="3" width="43.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="33" min="30" style="3" width="11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="43" min="34" style="4" width="11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16356" min="44" style="3" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16365" min="16357" style="3" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16369" min="16366" style="5" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16370" style="5" width="9.34"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="8" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AH1" s="6"/>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="6"/>
-      <c r="AK1" s="6"/>
-      <c r="AL1" s="6"/>
-      <c r="AM1" s="6"/>
-      <c r="AN1" s="6"/>
-      <c r="AO1" s="6"/>
-      <c r="AP1" s="6"/>
-      <c r="AQ1" s="6"/>
-      <c r="XEL1" s="7"/>
-      <c r="XEM1" s="0"/>
-      <c r="XEN1" s="0"/>
-      <c r="XEO1" s="0"/>
-      <c r="XEP1" s="0"/>
-      <c r="XEQ1" s="0"/>
-      <c r="XER1" s="0"/>
-      <c r="XES1" s="0"/>
-      <c r="XET1" s="0"/>
-      <c r="XEU1" s="0"/>
-      <c r="XEV1" s="0"/>
-      <c r="XEW1" s="0"/>
-      <c r="XEX1" s="0"/>
-      <c r="XEY1" s="0"/>
-      <c r="XEZ1" s="0"/>
-      <c r="XFA1" s="0"/>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="9"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="9"/>
+      <c r="AM1" s="9"/>
+      <c r="AN1" s="9"/>
+      <c r="AO1" s="9"/>
+      <c r="AP1" s="9"/>
+      <c r="AQ1" s="9"/>
+      <c r="XEL1" s="10"/>
+      <c r="XEM1" s="5"/>
+      <c r="XEN1" s="5"/>
+      <c r="XEO1" s="5"/>
+      <c r="XEP1" s="5"/>
+      <c r="XEQ1" s="5"/>
+      <c r="XER1" s="5"/>
+      <c r="XES1" s="5"/>
+      <c r="XET1" s="5"/>
+      <c r="XEU1" s="5"/>
+      <c r="XEV1" s="5"/>
+      <c r="XEW1" s="5"/>
+      <c r="XEX1" s="5"/>
+      <c r="XEY1" s="5"/>
+      <c r="XEZ1" s="5"/>
+      <c r="XFA1" s="5"/>
     </row>
-    <row r="2" s="11" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" s="13" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="10"/>
-      <c r="AH2" s="3"/>
-      <c r="AI2" s="3"/>
-      <c r="AJ2" s="3"/>
-      <c r="AK2" s="3"/>
-      <c r="AL2" s="3"/>
-      <c r="AM2" s="3"/>
-      <c r="AN2" s="3"/>
-      <c r="AO2" s="3"/>
-      <c r="AP2" s="3"/>
-      <c r="AQ2" s="3"/>
-      <c r="XEM2" s="0"/>
-      <c r="XEN2" s="0"/>
-      <c r="XEO2" s="0"/>
-      <c r="XEP2" s="0"/>
-      <c r="XEQ2" s="0"/>
-      <c r="XER2" s="0"/>
-      <c r="XES2" s="0"/>
-      <c r="XET2" s="0"/>
-      <c r="XEU2" s="0"/>
-      <c r="XEV2" s="0"/>
-      <c r="XEW2" s="0"/>
-      <c r="XEX2" s="0"/>
-      <c r="XEY2" s="0"/>
-      <c r="XEZ2" s="0"/>
-      <c r="XFA2" s="0"/>
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="11"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="12"/>
+      <c r="AH2" s="4"/>
+      <c r="AI2" s="4"/>
+      <c r="AJ2" s="4"/>
+      <c r="AK2" s="4"/>
+      <c r="AL2" s="4"/>
+      <c r="AM2" s="4"/>
+      <c r="AN2" s="4"/>
+      <c r="AO2" s="4"/>
+      <c r="AP2" s="4"/>
+      <c r="AQ2" s="4"/>
+      <c r="XEM2" s="5"/>
+      <c r="XEN2" s="5"/>
+      <c r="XEO2" s="5"/>
+      <c r="XEP2" s="5"/>
+      <c r="XEQ2" s="5"/>
+      <c r="XER2" s="5"/>
+      <c r="XES2" s="5"/>
+      <c r="XET2" s="5"/>
+      <c r="XEU2" s="5"/>
+      <c r="XEV2" s="5"/>
+      <c r="XEW2" s="5"/>
+      <c r="XEX2" s="5"/>
+      <c r="XEY2" s="5"/>
+      <c r="XEZ2" s="5"/>
+      <c r="XFA2" s="5"/>
     </row>
-    <row r="3" s="11" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="13" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3"/>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="3"/>
-      <c r="AL3" s="3"/>
-      <c r="AM3" s="3"/>
-      <c r="AN3" s="3"/>
-      <c r="AO3" s="3"/>
-      <c r="AP3" s="3"/>
-      <c r="AQ3" s="3"/>
-      <c r="XEM3" s="0"/>
-      <c r="XEN3" s="0"/>
-      <c r="XEO3" s="0"/>
-      <c r="XEP3" s="0"/>
-      <c r="XEQ3" s="0"/>
-      <c r="XER3" s="0"/>
-      <c r="XES3" s="0"/>
-      <c r="XET3" s="0"/>
-      <c r="XEU3" s="0"/>
-      <c r="XEV3" s="0"/>
-      <c r="XEW3" s="0"/>
-      <c r="XEX3" s="0"/>
-      <c r="XEY3" s="0"/>
-      <c r="XEZ3" s="0"/>
-      <c r="XFA3" s="0"/>
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH3" s="4"/>
+      <c r="AI3" s="4"/>
+      <c r="AJ3" s="4"/>
+      <c r="AK3" s="4"/>
+      <c r="AL3" s="4"/>
+      <c r="AM3" s="4"/>
+      <c r="AN3" s="4"/>
+      <c r="AO3" s="4"/>
+      <c r="AP3" s="4"/>
+      <c r="AQ3" s="4"/>
+      <c r="XEM3" s="5"/>
+      <c r="XEN3" s="5"/>
+      <c r="XEO3" s="5"/>
+      <c r="XEP3" s="5"/>
+      <c r="XEQ3" s="5"/>
+      <c r="XER3" s="5"/>
+      <c r="XES3" s="5"/>
+      <c r="XET3" s="5"/>
+      <c r="XEU3" s="5"/>
+      <c r="XEV3" s="5"/>
+      <c r="XEW3" s="5"/>
+      <c r="XEX3" s="5"/>
+      <c r="XEY3" s="5"/>
+      <c r="XEZ3" s="5"/>
+      <c r="XFA3" s="5"/>
     </row>
     <row r="1048517" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048518" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -796,7 +807,7 @@
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A1:XEK1" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A1:D1 F1:XEK1" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -824,68 +835,68 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="18.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="34.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="69.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="24.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="30.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="72.83"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="10" style="12" width="9.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16382" style="12" width="9.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="18.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="34.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="69.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="24.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="30.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="72.83"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="10" style="2" width="9.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16382" style="2" width="9.34"/>
   </cols>
   <sheetData>
-    <row r="1" s="13" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+    <row r="1" s="7" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="13" t="s">
+      <c r="B1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="13" t="s">
+      <c r="D1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="0"/>
-      <c r="H1" s="0"/>
-      <c r="I1" s="0"/>
+      <c r="F1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="12" t="s">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>18</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="12" t="s">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="12" t="s">
+      <c r="C3" s="2" t="s">
         <v>22</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
